--- a/WebHost/wwwroot/eam/basexlsx/施工能耗年度报表模板.xlsx
+++ b/WebHost/wwwroot/eam/basexlsx/施工能耗年度报表模板.xlsx
@@ -89,7 +89,7 @@
     <t>船次</t>
   </si>
   <si>
-    <t>作业时间</t>
+    <t>施工时间</t>
   </si>
   <si>
     <t>停工时间</t>
